--- a/test_data/login_credentials_sauce_demo.xlsx
+++ b/test_data/login_credentials_sauce_demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kaushal More\PythonAutomation\Frameworks\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5AB2EC-DC84-42CD-A7C9-C1812201EBAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF4E497-4FE0-4A75-A5EA-C6C077EF4607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="12">
   <si>
     <t>username</t>
   </si>
@@ -52,6 +52,15 @@
   </si>
   <si>
     <t>secret_sauce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">scenario </t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Negative</t>
   </si>
 </sst>
 </file>
@@ -152,13 +161,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,72 +449,93 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C1" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="C7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
-      <c r="B8" s="5"/>
+      <c r="B8" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
